--- a/data/trans_dic/P16A15-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A15-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,78</t>
+          <t>0,68; 2,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,52</t>
+          <t>0,15; 1,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,18</t>
+          <t>0,33; 2,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,14</t>
+          <t>0,21; 1,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,66</t>
+          <t>0,08; 0,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,13</t>
+          <t>0,68; 2,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,75</t>
+          <t>0,09; 0,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,32</t>
+          <t>0,22; 1,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,82</t>
+          <t>1,4; 3,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,13</t>
+          <t>2,28; 5,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,74</t>
+          <t>1,81; 4,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,0</t>
+          <t>1,81; 5,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,44</t>
+          <t>1,04; 3,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,15</t>
+          <t>1,67; 4,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,72</t>
+          <t>0,29; 1,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,76</t>
+          <t>0,47; 1,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,05</t>
+          <t>1,44; 3,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,08</t>
+          <t>2,17; 4,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,79</t>
+          <t>1,23; 2,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,92</t>
+          <t>1,26; 2,99</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,84</t>
+          <t>4,0; 7,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,34</t>
+          <t>5,84; 10,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,97</t>
+          <t>5,66; 10,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 10,39</t>
+          <t>2,82; 10,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,78</t>
+          <t>3,21; 6,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 11,64</t>
+          <t>6,75; 12,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,24</t>
+          <t>5,91; 10,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,26</t>
+          <t>4,17; 7,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,6</t>
+          <t>4,03; 6,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,46</t>
+          <t>6,86; 10,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,34</t>
+          <t>6,19; 9,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,07</t>
+          <t>3,94; 8,28</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,66; 17,43</t>
+          <t>10,71; 17,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,67; 23,94</t>
+          <t>15,75; 23,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,44; 19,5</t>
+          <t>12,47; 19,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,23; 23,27</t>
+          <t>17,4; 23,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,7; 19,02</t>
+          <t>11,62; 19,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,87; 27,47</t>
+          <t>18,6; 27,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,65; 24,38</t>
+          <t>16,41; 24,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,29; 23,39</t>
+          <t>18,19; 23,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,21; 16,93</t>
+          <t>11,96; 16,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 24,45</t>
+          <t>18,33; 24,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,75; 20,8</t>
+          <t>15,58; 20,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,22; 22,37</t>
+          <t>18,36; 22,59</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,38; 21,66</t>
+          <t>13,74; 21,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,45; 40,17</t>
+          <t>29,15; 40,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,69; 34,63</t>
+          <t>24,39; 34,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,11; 31,7</t>
+          <t>24,25; 31,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,92; 29,37</t>
+          <t>20,31; 29,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,83; 37,74</t>
+          <t>27,61; 37,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,5; 32,76</t>
+          <t>23,48; 33,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,5; 81,18</t>
+          <t>31,18; 79,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,29; 24,62</t>
+          <t>18,2; 24,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,09; 37,87</t>
+          <t>29,86; 37,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,53; 32,86</t>
+          <t>25,8; 32,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,56; 69,96</t>
+          <t>29,69; 71,07</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,41; 25,46</t>
+          <t>14,08; 24,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,74; 38,19</t>
+          <t>25,44; 38,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,57; 34,12</t>
+          <t>24,18; 34,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,42; 40,34</t>
+          <t>30,94; 40,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,17; 28,92</t>
+          <t>19,32; 29,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,36; 40,3</t>
+          <t>30,67; 40,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,26; 36,93</t>
+          <t>26,06; 36,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,51; 45,31</t>
+          <t>38,71; 45,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,63; 25,84</t>
+          <t>18,84; 26,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,02; 38,02</t>
+          <t>30,11; 38,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,03; 34,76</t>
+          <t>26,68; 34,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,55; 42,2</t>
+          <t>36,8; 42,0</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,64</t>
+          <t>5,02; 6,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,12; 11,3</t>
+          <t>9,24; 11,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,37</t>
+          <t>8,5; 10,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,97; 12,83</t>
+          <t>8,53; 12,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,05; 8,8</t>
+          <t>6,98; 8,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,16; 13,39</t>
+          <t>11,21; 13,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,91; 12,15</t>
+          <t>9,84; 12,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,43; 34,41</t>
+          <t>13,31; 32,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,52</t>
+          <t>6,32; 7,55</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,54; 12,07</t>
+          <t>10,5; 12,13</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,44; 10,98</t>
+          <t>9,45; 10,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,29; 24,35</t>
+          <t>12,19; 24,24</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1950</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1832</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1876</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9689</t>
+          <t>0; 9447</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1867</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1962</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 9960</t>
+          <t>0; 10981</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6742</t>
+          <t>0; 6984</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4430; 19048</t>
+          <t>4694; 20068</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>899; 8951</t>
+          <t>897; 8813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6409</t>
+          <t>0; 5351</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5901</t>
+          <t>0; 6642</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1874; 13280</t>
+          <t>1984; 14008</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4521</t>
+          <t>0; 5013</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1054; 10952</t>
+          <t>1082; 9508</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>944; 8958</t>
+          <t>1039; 9116</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9365; 27590</t>
+          <t>8795; 27842</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1015; 8692</t>
+          <t>1022; 9623</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2132; 12327</t>
+          <t>2064; 12094</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8475; 24327</t>
+          <t>8899; 24030</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14976; 34869</t>
+          <t>15515; 36087</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11944; 31719</t>
+          <t>12111; 31548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10019; 26844</t>
+          <t>9687; 27371</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7853; 23715</t>
+          <t>7205; 21977</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12362; 29328</t>
+          <t>11778; 28731</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1939; 11375</t>
+          <t>1887; 11082</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2538; 9554</t>
+          <t>2526; 9378</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19154; 40544</t>
+          <t>19162; 40405</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31674; 56532</t>
+          <t>30087; 57069</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16596; 37127</t>
+          <t>16365; 36732</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13947; 31489</t>
+          <t>13587; 32297</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20337; 40689</t>
+          <t>20761; 41105</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36064; 63531</t>
+          <t>35896; 65465</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36453; 64427</t>
+          <t>36554; 65283</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27469; 92240</t>
+          <t>25013; 93353</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16727; 34960</t>
+          <t>16572; 34878</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40753; 71487</t>
+          <t>41465; 73987</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39168; 66448</t>
+          <t>38357; 65400</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31213; 51742</t>
+          <t>29758; 50838</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41405; 68335</t>
+          <t>41752; 70345</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>86273; 128511</t>
+          <t>84253; 127699</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82395; 121014</t>
+          <t>80168; 119137</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54232; 129193</t>
+          <t>63068; 132568</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41216; 67407</t>
+          <t>41423; 66783</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67006; 102356</t>
+          <t>67317; 101461</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59445; 93215</t>
+          <t>59604; 92326</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96552; 130347</t>
+          <t>97471; 132664</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47259; 76858</t>
+          <t>46925; 77002</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84307; 122734</t>
+          <t>83089; 122246</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82743; 121131</t>
+          <t>81549; 120589</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99665; 127452</t>
+          <t>99108; 126212</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>96516; 133833</t>
+          <t>94606; 132595</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>160278; 213794</t>
+          <t>160250; 211208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>153560; 202705</t>
+          <t>151907; 202086</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>201404; 247225</t>
+          <t>202908; 249620</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39133; 63375</t>
+          <t>40208; 64283</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88130; 124431</t>
+          <t>90292; 124932</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82542; 115762</t>
+          <t>81555; 114897</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88765; 116721</t>
+          <t>89274; 116980</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71731; 100731</t>
+          <t>69653; 100949</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>98525; 133610</t>
+          <t>97745; 133183</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>88760; 123738</t>
+          <t>88717; 126019</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>191651; 493851</t>
+          <t>189705; 482778</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>116215; 156495</t>
+          <t>115649; 158390</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>199709; 251401</t>
+          <t>198186; 250441</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181795; 233963</t>
+          <t>183746; 233163</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>288706; 683190</t>
+          <t>289958; 694020</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>30253; 53436</t>
+          <t>29556; 52069</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64304; 95409</t>
+          <t>63574; 96569</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>63135; 87683</t>
+          <t>62147; 88488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88854; 114071</t>
+          <t>87486; 113936</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>63995; 96566</t>
+          <t>64515; 98697</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>117406; 155850</t>
+          <t>118610; 156107</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>105103; 147766</t>
+          <t>104291; 145680</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>163557; 192429</t>
+          <t>164432; 192120</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>101323; 140498</t>
+          <t>102447; 141502</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>191124; 242013</t>
+          <t>191664; 244335</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>177615; 228446</t>
+          <t>175317; 225281</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>258567; 298565</t>
+          <t>260360; 297150</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>164412; 217366</t>
+          <t>164340; 218178</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>311936; 386535</t>
+          <t>315960; 387073</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>283875; 351976</t>
+          <t>288562; 356536</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>310253; 443635</t>
+          <t>294988; 442832</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>238111; 297241</t>
+          <t>235995; 297745</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>395711; 474950</t>
+          <t>397571; 482700</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>351406; 430726</t>
+          <t>348835; 426247</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>491218; 1258568</t>
+          <t>486816; 1202240</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>413344; 500464</t>
+          <t>420869; 502330</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>734156; 840868</t>
+          <t>731552; 845405</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>655378; 761595</t>
+          <t>655952; 761295</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>874918; 1732706</t>
+          <t>867714; 1724811</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A15-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A15-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
     </row>
@@ -804,14 +804,14 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,92</t>
+          <t>0,67; 2,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,49</t>
+          <t>0,15; 1,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,3</t>
+          <t>0,32; 2,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,86</t>
+          <t>0,2; 1,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,67</t>
+          <t>0,07; 0,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,15</t>
+          <t>0,68; 2,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,83</t>
+          <t>0,09; 0,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,29</t>
+          <t>0,2; 1,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,77</t>
+          <t>1,29; 3,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,31</t>
+          <t>2,23; 5,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,71</t>
+          <t>1,82; 4,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,1</t>
+          <t>2,08; 5,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,19</t>
+          <t>0,98; 3,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,07</t>
+          <t>1,73; 4,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,68</t>
+          <t>0,37; 1,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,73</t>
+          <t>0,71; 2,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,04</t>
+          <t>1,47; 3,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,12</t>
+          <t>2,19; 4,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,76</t>
+          <t>1,23; 2,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,99</t>
+          <t>1,51; 3,27</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,92</t>
+          <t>3,86; 7,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,65</t>
+          <t>6,08; 10,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,1</t>
+          <t>5,66; 9,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,52</t>
+          <t>7,13; 11,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,76</t>
+          <t>3,11; 6,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 12,05</t>
+          <t>6,86; 11,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,08</t>
+          <t>5,94; 10,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,13</t>
+          <t>4,63; 7,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,8</t>
+          <t>4,03; 6,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,39</t>
+          <t>6,98; 10,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,2</t>
+          <t>6,39; 9,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 8,28</t>
+          <t>6,28; 8,97</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,71; 17,27</t>
+          <t>10,36; 17,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,75; 23,73</t>
+          <t>15,63; 23,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,47; 19,32</t>
+          <t>12,58; 19,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,4; 23,68</t>
+          <t>16,1; 22,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,62; 19,06</t>
+          <t>11,49; 18,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,6; 27,36</t>
+          <t>18,66; 26,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,41; 24,27</t>
+          <t>16,81; 24,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,19; 23,16</t>
+          <t>18,29; 23,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,96; 16,77</t>
+          <t>12,1; 17,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 24,16</t>
+          <t>18,3; 23,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,58; 20,73</t>
+          <t>15,37; 20,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,36; 22,59</t>
+          <t>18,07; 21,92</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,74; 21,97</t>
+          <t>13,63; 22,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,15; 40,33</t>
+          <t>29,18; 40,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,39; 34,37</t>
+          <t>24,61; 34,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,25; 31,77</t>
+          <t>23,75; 31,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,31; 29,44</t>
+          <t>20,73; 29,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,61; 37,62</t>
+          <t>27,57; 37,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,48; 33,36</t>
+          <t>23,41; 33,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,18; 79,36</t>
+          <t>29,48; 35,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,2; 24,92</t>
+          <t>18,49; 24,47</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,86; 37,73</t>
+          <t>29,63; 37,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,8; 32,74</t>
+          <t>25,66; 32,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,69; 71,07</t>
+          <t>27,66; 32,66</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,08; 24,81</t>
+          <t>14,15; 24,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,44; 38,65</t>
+          <t>25,51; 37,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,18; 34,43</t>
+          <t>24,29; 34,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,94; 40,29</t>
+          <t>30,97; 40,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,32; 29,56</t>
+          <t>19,69; 29,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,67; 40,37</t>
+          <t>30,37; 40,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,06; 36,4</t>
+          <t>25,99; 36,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,71; 45,23</t>
+          <t>38,26; 44,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,84; 26,02</t>
+          <t>19,01; 26,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,11; 38,38</t>
+          <t>30,29; 37,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26,68; 34,28</t>
+          <t>26,91; 33,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,8; 42,0</t>
+          <t>36,42; 41,52</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,66</t>
+          <t>5,02; 6,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,24; 11,31</t>
+          <t>9,3; 11,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,5; 10,5</t>
+          <t>8,36; 10,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,8</t>
+          <t>11,04; 12,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,81</t>
+          <t>7,0; 8,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,21; 13,61</t>
+          <t>11,21; 13,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,84; 12,03</t>
+          <t>10,02; 12,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,31; 32,87</t>
+          <t>13,03; 14,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,32; 7,55</t>
+          <t>6,31; 7,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,5; 12,13</t>
+          <t>10,59; 12,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,45; 10,97</t>
+          <t>9,47; 10,99</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,19; 24,24</t>
+          <t>12,28; 13,68</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3137</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9447</t>
+          <t>0; 12232</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 10981</t>
+          <t>0; 12427</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5598</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6984</t>
+          <t>0; 5959</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4694; 20068</t>
+          <t>4611; 20050</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>897; 8813</t>
+          <t>899; 8029</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5351</t>
+          <t>0; 7436</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6642</t>
+          <t>0; 6346</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1984; 14008</t>
+          <t>1961; 12838</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5013</t>
+          <t>0; 4545</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1082; 9508</t>
+          <t>1021; 9823</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1039; 9116</t>
+          <t>1010; 8967</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8795; 27842</t>
+          <t>8804; 28163</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1022; 9623</t>
+          <t>1018; 9749</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2064; 12094</t>
+          <t>1993; 13697</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>28351</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8899; 24030</t>
+          <t>8235; 23870</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15515; 36087</t>
+          <t>15185; 34439</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12111; 31548</t>
+          <t>12191; 30308</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9687; 27371</t>
+          <t>12912; 31660</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7205; 21977</t>
+          <t>6770; 22018</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11778; 28731</t>
+          <t>12245; 29695</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1887; 11082</t>
+          <t>2432; 10717</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2526; 9378</t>
+          <t>4436; 14419</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19162; 40405</t>
+          <t>19518; 42132</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30087; 57069</t>
+          <t>30366; 56788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16365; 36732</t>
+          <t>16415; 36535</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13587; 32297</t>
+          <t>18807; 40616</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61551</t>
+          <t>63686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>43363</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>102072</t>
+          <t>107049</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20761; 41105</t>
+          <t>20059; 39961</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35896; 65465</t>
+          <t>37352; 65090</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36554; 65283</t>
+          <t>36589; 64513</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25013; 93353</t>
+          <t>49966; 82949</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16572; 34878</t>
+          <t>16018; 35785</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41465; 73987</t>
+          <t>42106; 73319</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38357; 65400</t>
+          <t>38551; 65362</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29758; 50838</t>
+          <t>34104; 53789</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41752; 70345</t>
+          <t>41693; 68869</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84253; 127699</t>
+          <t>85744; 129313</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>80168; 119137</t>
+          <t>82739; 120881</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63068; 132568</t>
+          <t>90268; 128899</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112954</t>
+          <t>116920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>112339</t>
+          <t>124622</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>225293</t>
+          <t>241542</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41423; 66783</t>
+          <t>40079; 66921</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67317; 101461</t>
+          <t>66839; 101682</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59604; 92326</t>
+          <t>60125; 93871</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>97471; 132664</t>
+          <t>97946; 136471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>46925; 77002</t>
+          <t>46430; 76498</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83089; 122246</t>
+          <t>83372; 119338</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81549; 120589</t>
+          <t>83502; 119362</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99108; 126212</t>
+          <t>111100; 143185</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>94606; 132595</t>
+          <t>95689; 136111</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>160250; 211208</t>
+          <t>159962; 209499</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>151907; 202086</t>
+          <t>149857; 199545</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>202908; 249620</t>
+          <t>219709; 266539</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103026</t>
+          <t>111454</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>335912</t>
+          <t>143186</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>438938</t>
+          <t>254640</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40208; 64283</t>
+          <t>39884; 65148</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>90292; 124932</t>
+          <t>90398; 125471</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81555; 114897</t>
+          <t>82272; 115242</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89274; 116980</t>
+          <t>96697; 126989</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>69653; 100949</t>
+          <t>71099; 101311</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>97745; 133183</t>
+          <t>97589; 133573</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>88717; 126019</t>
+          <t>88452; 125354</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>189705; 482778</t>
+          <t>129453; 157607</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>115649; 158390</t>
+          <t>117505; 155497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>198186; 250441</t>
+          <t>196679; 247818</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>183746; 233163</t>
+          <t>182732; 229713</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>289958; 694020</t>
+          <t>234049; 276413</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>100424</t>
+          <t>109806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>177784</t>
+          <t>191701</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>278208</t>
+          <t>301507</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29556; 52069</t>
+          <t>29699; 51947</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>63574; 96569</t>
+          <t>63742; 94221</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>62147; 88488</t>
+          <t>62414; 87825</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87486; 113936</t>
+          <t>96078; 125008</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>64515; 98697</t>
+          <t>65757; 98257</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>118610; 156107</t>
+          <t>117462; 156701</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>104291; 145680</t>
+          <t>104012; 145341</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>164432; 192120</t>
+          <t>177301; 207115</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>102447; 141502</t>
+          <t>103401; 141953</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>191664; 244335</t>
+          <t>192821; 240963</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>175317; 225281</t>
+          <t>176822; 222604</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>260360; 297150</t>
+          <t>281781; 321186</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>395938</t>
+          <t>423495</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>678408</t>
+          <t>518329</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1074346</t>
+          <t>941824</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>164340; 218178</t>
+          <t>164565; 216536</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>315960; 387073</t>
+          <t>318298; 393069</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>288562; 356536</t>
+          <t>283741; 351265</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>294988; 442832</t>
+          <t>390015; 458262</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>235995; 297745</t>
+          <t>236389; 297601</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>397571; 482700</t>
+          <t>397636; 475543</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>348835; 426247</t>
+          <t>355114; 430273</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>486816; 1202240</t>
+          <t>486233; 551151</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>420869; 502330</t>
+          <t>419808; 496259</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>731552; 845405</t>
+          <t>738161; 841006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>655952; 761295</t>
+          <t>657075; 762250</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>867714; 1724811</t>
+          <t>891729; 993896</t>
         </is>
       </c>
     </row>
